--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484128_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484128_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. SENGHOR</t>
+          <t>M. BUSCAIL BRIANSO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2087</v>
+        <v>4.9413</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5656</v>
+        <v>1.9699</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6431</v>
+        <v>2.9714</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5826</v>
+        <v>6.4669</v>
       </c>
       <c r="H2" t="n">
-        <v>2.6811</v>
+        <v>4.8033</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0984</v>
+        <v>1.6636</v>
       </c>
       <c r="J2" t="n">
-        <v>3.891</v>
+        <v>5.4084</v>
       </c>
       <c r="K2" t="n">
-        <v>3.2057</v>
+        <v>4.0429</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6853</v>
+        <v>1.3655</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.3083</v>
+        <v>1.0585</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5246</v>
+        <v>0.7604</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.7837</v>
+        <v>0.2981</v>
       </c>
       <c r="P2" t="n">
-        <v>1.3887</v>
+        <v>-2.1822</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-3.9677</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3887</v>
+        <v>1.7855</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5629</v>
+        <v>-0.2126</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6746</v>
+        <v>-0.34</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1117</v>
+        <v>0.1274</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6745</v>
+        <v>0.8692</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>0.8692</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. HALL</t>
+          <t>A. SENGHOR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6142</v>
+        <v>4.6246</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4822</v>
+        <v>3.9534</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8681</v>
+        <v>0.6712</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4191</v>
+        <v>2.5826</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7209</v>
+        <v>2.6811</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3018</v>
+        <v>-0.0984</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6635</v>
+        <v>3.891</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5832</v>
+        <v>3.2057</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0803</v>
+        <v>0.6853</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.2444</v>
+        <v>-1.3083</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8623</v>
+        <v>-0.5246</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3821</v>
+        <v>-0.7837</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3968</v>
+        <v>1.3887</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1984</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5952</v>
+        <v>1.3887</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3853</v>
+        <v>-0.0213</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6042</v>
+        <v>0.0624</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2188</v>
+        <v>-0.0837</v>
       </c>
       <c r="V3" t="n">
-        <v>2.4129</v>
+        <v>0.6745</v>
       </c>
       <c r="W3" t="n">
-        <v>2.4129</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. BUSCAIL BRIANSO</t>
+          <t>D. FERNANDEZ LINARES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5893</v>
+        <v>4.3652</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5618</v>
+        <v>2.9373</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0275</v>
+        <v>1.4279</v>
       </c>
       <c r="G4" t="n">
-        <v>6.4669</v>
+        <v>2.5868</v>
       </c>
       <c r="H4" t="n">
-        <v>4.8033</v>
+        <v>1.2394</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6636</v>
+        <v>1.3474</v>
       </c>
       <c r="J4" t="n">
-        <v>5.4084</v>
+        <v>2.7445</v>
       </c>
       <c r="K4" t="n">
-        <v>4.0429</v>
+        <v>2.0968</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3655</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0585</v>
+        <v>-0.1577</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7604</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2981</v>
+        <v>0.6997</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.1822</v>
+        <v>1.3887</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.9677</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7855</v>
+        <v>1.3887</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5646</v>
+        <v>0.3897</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7481</v>
+        <v>0.1928</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1835</v>
+        <v>0.1969</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8692</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8692</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. LORAS MONTERO</t>
+          <t>S. HALL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.7824</v>
+        <v>3.9203</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4031</v>
+        <v>4.564</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3793</v>
+        <v>-0.6435999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6437</v>
+        <v>0.4191</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5348000000000001</v>
+        <v>0.7209</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1089</v>
+        <v>-0.3018</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2734</v>
+        <v>1.6635</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1906</v>
+        <v>1.5832</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0829</v>
+        <v>0.0803</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6298</v>
+        <v>-1.2444</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6558</v>
+        <v>-0.8623</v>
       </c>
       <c r="O5" t="n">
-        <v>0.026</v>
+        <v>-0.3821</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.7855</v>
+        <v>0.3968</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.1741</v>
+        <v>-0.1984</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3887</v>
+        <v>0.5952</v>
       </c>
       <c r="S5" t="n">
-        <v>3.7177</v>
+        <v>0.6915</v>
       </c>
       <c r="T5" t="n">
-        <v>2.0973</v>
+        <v>0.6859</v>
       </c>
       <c r="U5" t="n">
-        <v>1.6203</v>
+        <v>0.0056</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2065</v>
+        <v>2.4129</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2065</v>
+        <v>2.4129</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ LINARES</t>
+          <t>D. FERNANDEZ STEFANUTO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.1281</v>
+        <v>2.7269</v>
       </c>
       <c r="E6" t="n">
-        <v>2.121</v>
+        <v>0.6195000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>1.007</v>
+        <v>2.1074</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5868</v>
+        <v>0.95</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2394</v>
+        <v>-0.5891999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3474</v>
+        <v>1.5391</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7445</v>
+        <v>1.2486</v>
       </c>
       <c r="K6" t="n">
-        <v>2.0968</v>
+        <v>0.001</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6477000000000001</v>
+        <v>1.2476</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1577</v>
+        <v>-0.2986</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6997</v>
+        <v>0.2916</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3887</v>
+        <v>0.7935</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3887</v>
+        <v>1.7855</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8474</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6235000000000001</v>
+        <v>0.3628</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.224</v>
+        <v>0.6206</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ STEFANUTO</t>
+          <t>D. LORAS MONTERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.3647</v>
+        <v>1.8005</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3134</v>
+        <v>0.1787</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0513</v>
+        <v>1.6218</v>
       </c>
       <c r="G7" t="n">
-        <v>0.95</v>
+        <v>0.6437</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5891999999999999</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5391</v>
+        <v>0.1089</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2486</v>
+        <v>1.2734</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001</v>
+        <v>1.1906</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2476</v>
+        <v>0.0829</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2986</v>
+        <v>-0.6298</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5901999999999999</v>
+        <v>-0.6558</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2916</v>
+        <v>0.026</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7935</v>
+        <v>-1.7855</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9919</v>
+        <v>-3.1741</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7855</v>
+        <v>1.3887</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6212</v>
+        <v>1.7358</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0567</v>
+        <v>0.873</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5645</v>
+        <v>0.8628</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. ROSET CLAVERO</t>
+          <t>T. KOHAN LÓPEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7741</v>
+        <v>1.0559</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1442</v>
+        <v>1.2767</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9183</v>
+        <v>-0.2207</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3539</v>
+        <v>0.6663</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1812</v>
+        <v>0.2918</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5351</v>
+        <v>0.3745</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6373</v>
+        <v>1.8321</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0403</v>
+        <v>0.5444</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6776</v>
+        <v>1.2877</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2835</v>
+        <v>-1.1658</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1409</v>
+        <v>-0.2525</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1425</v>
+        <v>-0.9133</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3968</v>
+        <v>0.7935</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.1984</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3968</v>
+        <v>0.9919</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7312</v>
+        <v>-1.0784</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4932</v>
+        <v>-0.357</v>
       </c>
       <c r="U8" t="n">
-        <v>0.238</v>
+        <v>-0.7214</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.6745</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. KOHAN LÓPEZ</t>
+          <t>J. ROSET CLAVERO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6555</v>
+        <v>0.57</v>
       </c>
       <c r="E9" t="n">
-        <v>1.0726</v>
+        <v>-0.3482</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4171</v>
+        <v>0.9183</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6663</v>
+        <v>-0.3539</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2918</v>
+        <v>0.1812</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3745</v>
+        <v>-0.5351</v>
       </c>
       <c r="J9" t="n">
-        <v>1.8321</v>
+        <v>-0.6373</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5444</v>
+        <v>0.0403</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2877</v>
+        <v>-0.6776</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1658</v>
+        <v>0.2835</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2525</v>
+        <v>0.1409</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9133</v>
+        <v>0.1425</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7935</v>
+        <v>0.3968</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1984</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9919</v>
+        <v>0.3968</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4788</v>
+        <v>0.5271</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5611</v>
+        <v>0.2891</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9177</v>
+        <v>0.238</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6745</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9187</v>
+        <v>-0.3882</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2604</v>
+        <v>-0.9543</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3417</v>
+        <v>0.5661</v>
       </c>
       <c r="G10" t="n">
         <v>0.9268</v>
@@ -1234,13 +1234,13 @@
         <v>0.7935</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6553</v>
+        <v>-0.1247</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4988</v>
+        <v>-0.1927</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1565</v>
+        <v>0.0679</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6549</v>
+        <v>-2.2952</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.4037</v>
+        <v>-3.7915</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7487</v>
+        <v>1.4962</v>
       </c>
       <c r="G11" t="n">
         <v>-1.1096</v>
@@ -1312,13 +1312,13 @@
         <v>1.3887</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3077</v>
+        <v>0.6674</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4988</v>
+        <v>0.1134</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8065</v>
+        <v>0.554</v>
       </c>
       <c r="V11" t="n">
         <v>-0.266</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2184</v>
+        <v>-2.772</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8633999999999999</v>
+        <v>-0.5574</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3549</v>
+        <v>-2.2146</v>
       </c>
       <c r="G12" t="n">
         <v>0.8801</v>
@@ -1390,13 +1390,13 @@
         <v>0.7935</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3292</v>
+        <v>-0.8829</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7481</v>
+        <v>-0.4421</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5810999999999999</v>
+        <v>-0.4408</v>
       </c>
       <c r="V12" t="n">
         <v>0.6032</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.7764</v>
+        <v>-4.0008</v>
       </c>
       <c r="E13" t="n">
         <v>-2.7616</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0148</v>
+        <v>-1.2392</v>
       </c>
       <c r="G13" t="n">
         <v>-2.4482</v>
@@ -1468,13 +1468,13 @@
         <v>0.1984</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0703</v>
+        <v>-0.2948</v>
       </c>
       <c r="T13" t="n">
         <v>-0.3117</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2414</v>
+        <v>0.017</v>
       </c>
       <c r="V13" t="n">
         <v>-0.266</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>14.5486</v>
+        <v>14.5485</v>
       </c>
       <c r="E14" t="n">
-        <v>7.086399999999998</v>
+        <v>7.086500000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>7.461999999999999</v>
+        <v>7.462199999999999</v>
       </c>
       <c r="G14" t="n">
         <v>12.2106</v>
@@ -1516,7 +1516,7 @@
         <v>12.8259</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6150999999999995</v>
+        <v>-0.6151000000000004</v>
       </c>
       <c r="J14" t="n">
         <v>17.4923</v>
@@ -1546,13 +1546,13 @@
         <v>12.8951</v>
       </c>
       <c r="S14" t="n">
-        <v>2.3804</v>
+        <v>2.3802</v>
       </c>
       <c r="T14" t="n">
         <v>0.9358999999999998</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4444</v>
+        <v>1.4443</v>
       </c>
       <c r="V14" t="n">
         <v>5.9088</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.053</v>
+        <v>1.7291</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6518</v>
+        <v>0.2437</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4012</v>
+        <v>1.4854</v>
       </c>
       <c r="G15" t="n">
         <v>-0.0437</v>
@@ -1624,13 +1624,13 @@
         <v>2.579</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5096000000000001</v>
+        <v>0.1857</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3742</v>
+        <v>-0.0339</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1354</v>
+        <v>0.2196</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3636</v>
+        <v>0.5039</v>
       </c>
       <c r="E16" t="n">
         <v>0.6497000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2861</v>
+        <v>-0.1458</v>
       </c>
       <c r="G16" t="n">
         <v>-0.7045</v>
@@ -1702,13 +1702,13 @@
         <v>1.5871</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8815</v>
+        <v>1.0217</v>
       </c>
       <c r="T16" t="n">
         <v>0.4366</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4449</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>-0.4085</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. MALARY</t>
+          <t>A. PIQUERAS CARBONELL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2637</v>
+        <v>0.1768</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2512</v>
+        <v>0.0177</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.9875</v>
+        <v>0.1591</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1256</v>
+        <v>-0.2908</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0639</v>
+        <v>-0.1613</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.1895</v>
+        <v>-0.1295</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9089</v>
+        <v>0.0403</v>
       </c>
       <c r="K17" t="n">
-        <v>3.3277</v>
+        <v>0.0403</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.4188</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.0345</v>
+        <v>-0.3312</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.2638</v>
+        <v>-0.2016</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.1295</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1984</v>
+        <v>0.3968</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7774</v>
+        <v>0.3968</v>
       </c>
       <c r="S17" t="n">
-        <v>1.5282</v>
+        <v>0.0709</v>
       </c>
       <c r="T17" t="n">
-        <v>2.0521</v>
+        <v>-0.0227</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5238</v>
+        <v>0.0935</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9405</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. PIQUERAS CARBONELL</t>
+          <t>M. MANYOSES ROCA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0187</v>
+        <v>-0.1707</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0844</v>
+        <v>-0.3416</v>
       </c>
       <c r="F18" t="n">
-        <v>0.103</v>
+        <v>0.1709</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2908</v>
+        <v>-0.8225</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1613</v>
+        <v>-0.3782</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1295</v>
+        <v>-0.4443</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0403</v>
+        <v>0.1005</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0403</v>
+        <v>0.0202</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.0803</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3312</v>
+        <v>-0.923</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2016</v>
+        <v>-0.3983</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1295</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3968</v>
+        <v>1.1903</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3968</v>
+        <v>1.1903</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0873</v>
+        <v>-0.5384</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1247</v>
+        <v>-0.4421</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0374</v>
+        <v>-0.0964</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. MANYOSES ROCA</t>
+          <t>R. GUILLEN PILCO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4767</v>
+        <v>-0.6837</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-1.6143</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1709</v>
+        <v>0.9306</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8225</v>
+        <v>-1.8783</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3782</v>
+        <v>-1.1087</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4443</v>
+        <v>-0.7696</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1005</v>
+        <v>-1.2799</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0202</v>
+        <v>-0.6399</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0803</v>
+        <v>-0.64</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.923</v>
+        <v>-0.5983000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3983</v>
+        <v>-0.4688</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.1295</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1903</v>
+        <v>1.3887</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1903</v>
+        <v>1.3887</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8445</v>
+        <v>-0.1941</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7481</v>
+        <v>-0.3344</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0964</v>
+        <v>0.1403</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. GUILLEN PILCO</t>
+          <t>L. MALARY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8699</v>
+        <v>-1.2106</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7163</v>
+        <v>0.7207</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8465</v>
+        <v>-1.9314</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.8783</v>
+        <v>-0.1256</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1087</v>
+        <v>1.0639</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7696</v>
+        <v>-1.1895</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.2799</v>
+        <v>2.9089</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6399</v>
+        <v>3.3277</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.64</v>
+        <v>-0.4188</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-3.0345</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4688</v>
+        <v>-2.2638</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1295</v>
+        <v>-0.7707000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>1.3887</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.9758</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3887</v>
+        <v>2.7774</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3803</v>
+        <v>0.0539</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4364</v>
+        <v>0.5216</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0561</v>
+        <v>-0.4677</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.9405</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5612</v>
+        <v>-1.4872</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1452</v>
+        <v>0.2472</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7064</v>
+        <v>-1.7344</v>
       </c>
       <c r="G21" t="n">
         <v>1.2701</v>
@@ -2092,13 +2092,13 @@
         <v>2.3806</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4778</v>
+        <v>-0.4038</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.306</v>
+        <v>-0.2039</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1718</v>
+        <v>-0.1999</v>
       </c>
       <c r="V21" t="n">
         <v>-2.7502</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7377</v>
+        <v>-2.4698</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3185</v>
+        <v>1.7266</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.0561</v>
+        <v>-4.1964</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2166</v>
@@ -2170,13 +2170,13 @@
         <v>1.3887</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.7033</v>
+        <v>-1.4354</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0485</v>
+        <v>-0.6404</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6548</v>
+        <v>-0.795</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2065</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0315</v>
+        <v>-3.9754</v>
       </c>
       <c r="E23" t="n">
         <v>-4.6715</v>
       </c>
       <c r="F23" t="n">
-        <v>0.64</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="G23" t="n">
         <v>-4.0567</v>
@@ -2248,13 +2248,13 @@
         <v>2.7774</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9828</v>
+        <v>-0.9267</v>
       </c>
       <c r="T23" t="n">
         <v>-0.4193</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5635</v>
+        <v>-0.5074</v>
       </c>
       <c r="V23" t="n">
         <v>1.2065</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.5706</v>
+        <v>-6.9609</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.3585</v>
+        <v>-4.4403</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.212</v>
+        <v>-2.5207</v>
       </c>
       <c r="G24" t="n">
         <v>-4.3422</v>
@@ -2326,13 +2326,13 @@
         <v>2.3806</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8236</v>
+        <v>-0.2139</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.2242</v>
+        <v>-0.3059</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4006</v>
+        <v>0.092</v>
       </c>
       <c r="V24" t="n">
         <v>-1.8097</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-14.5486</v>
+        <v>-14.5485</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.462</v>
+        <v>-7.4621</v>
       </c>
       <c r="F25" t="n">
-        <v>-7.086499999999999</v>
+        <v>-7.086599999999999</v>
       </c>
       <c r="G25" t="n">
         <v>-12.2108</v>
@@ -2395,7 +2395,7 @@
         <v>-1.8131</v>
       </c>
       <c r="P25" t="n">
-        <v>5.951599999999998</v>
+        <v>5.9516</v>
       </c>
       <c r="Q25" t="n">
         <v>-12.895</v>
@@ -2404,13 +2404,13 @@
         <v>18.8466</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.3803</v>
+        <v>-2.3801</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.4443</v>
+        <v>-1.4444</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.9359</v>
+        <v>-0.9358000000000001</v>
       </c>
       <c r="V25" t="n">
         <v>-5.9089</v>
